--- a/Eric_fonctionnel_correction_bugs/ig/all-profiles.xlsx
+++ b/Eric_fonctionnel_correction_bugs/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:55:40+00:00</t>
+    <t>2024-07-25T08:10:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric_fonctionnel_correction_bugs/ig/all-profiles.xlsx
+++ b/Eric_fonctionnel_correction_bugs/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T08:10:32+00:00</t>
+    <t>2024-07-25T08:29:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric_fonctionnel_correction_bugs/ig/all-profiles.xlsx
+++ b/Eric_fonctionnel_correction_bugs/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T08:29:19+00:00</t>
+    <t>2024-07-25T08:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric_fonctionnel_correction_bugs/ig/all-profiles.xlsx
+++ b/Eric_fonctionnel_correction_bugs/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T08:44:44+00:00</t>
+    <t>2024-07-25T08:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
